--- a/site/exports/Texas_Surplus_Feed.xlsx
+++ b/site/exports/Texas_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>

--- a/site/exports/Texas_Surplus_Feed.xlsx
+++ b/site/exports/Texas_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>

--- a/site/exports/Texas_Surplus_Feed.xlsx
+++ b/site/exports/Texas_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>https://www.hcdistrictclerk.com/</t>
+          <t>https://www.hcdistrictclerk.com/edocs/public/CaseDetails.aspx?Cas=2024-TX-04812</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>https://www.hcdistrictclerk.com/</t>
+          <t>https://www.hcdistrictclerk.com/edocs/public/CaseDetails.aspx?Cas=2024-TX-04950</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/</t>
+          <t>https://www.dallascounty.org/government/district-clerk/tax-foreclosures.php?case=2024-TX-02044</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/</t>
+          <t>https://www.dallascounty.org/government/district-clerk/tax-foreclosures.php?case=2024-TX-01928</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>https://www.hcdistrictclerk.com/</t>
+          <t>https://www.hcdistrictclerk.com/edocs/public/CaseDetails.aspx?Cas=2024-TX-05110</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>

--- a/site/exports/Texas_Surplus_Feed.xlsx
+++ b/site/exports/Texas_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>https://www.hcdistrictclerk.com/edocs/public/CaseDetails.aspx?Cas=2024-TX-04812</t>
+          <t>https://www.hcdistrictclerk.com/</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>https://www.hcdistrictclerk.com/edocs/public/CaseDetails.aspx?Cas=2024-TX-04950</t>
+          <t>https://www.hcdistrictclerk.com/</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/government/district-clerk/tax-foreclosures.php?case=2024-TX-02044</t>
+          <t>https://www.dallascounty.org/</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/government/district-clerk/tax-foreclosures.php?case=2024-TX-01928</t>
+          <t>https://www.dallascounty.org/</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>https://www.hcdistrictclerk.com/edocs/public/CaseDetails.aspx?Cas=2024-TX-05110</t>
+          <t>https://www.hcdistrictclerk.com/</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>

--- a/site/exports/Texas_Surplus_Feed.xlsx
+++ b/site/exports/Texas_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>https://www.hcdistrictclerk.com/</t>
+          <t>https://www.hcdistrictclerk.com/edocs/public/CaseDetails.aspx?Cas=2024-TX-04812</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>https://www.hcdistrictclerk.com/</t>
+          <t>https://www.hcdistrictclerk.com/edocs/public/CaseDetails.aspx?Cas=2024-TX-04950</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/</t>
+          <t>https://www.dallascounty.org/government/county-clerk/recording/foreclosures.php?case=2024-TX-02044</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/</t>
+          <t>https://www.dallascounty.org/government/county-clerk/recording/foreclosures.php?case=2024-TX-01928</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>https://www.hcdistrictclerk.com/</t>
+          <t>https://www.hcdistrictclerk.com/edocs/public/CaseDetails.aspx?Cas=2024-TX-05110</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>

--- a/site/exports/Texas_Surplus_Feed.xlsx
+++ b/site/exports/Texas_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>

--- a/site/exports/Texas_Surplus_Feed.xlsx
+++ b/site/exports/Texas_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>

--- a/site/exports/Texas_Surplus_Feed.xlsx
+++ b/site/exports/Texas_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>

--- a/site/exports/Texas_Surplus_Feed.xlsx
+++ b/site/exports/Texas_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>

--- a/site/exports/Texas_Surplus_Feed.xlsx
+++ b/site/exports/Texas_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>

--- a/site/exports/Texas_Surplus_Feed.xlsx
+++ b/site/exports/Texas_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>

--- a/site/exports/Texas_Surplus_Feed.xlsx
+++ b/site/exports/Texas_Surplus_Feed.xlsx
@@ -682,7 +682,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2602,7 +2602,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3498,7 +3498,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3754,7 +3754,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -4138,7 +4138,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -4266,7 +4266,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -4394,7 +4394,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -4522,7 +4522,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -4778,7 +4778,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -4906,7 +4906,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5034,7 +5034,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5162,7 +5162,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5546,7 +5546,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6698,7 +6698,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7210,7 +7210,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7466,7 +7466,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7850,7 +7850,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -8106,7 +8106,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -8234,7 +8234,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -8362,7 +8362,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -8618,7 +8618,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -8746,7 +8746,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9002,7 +9002,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9130,7 +9130,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9258,7 +9258,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9386,7 +9386,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9514,7 +9514,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9642,7 +9642,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9770,7 +9770,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9898,7 +9898,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10026,7 +10026,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10154,7 +10154,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10282,7 +10282,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10410,7 +10410,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10538,7 +10538,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10666,7 +10666,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10794,7 +10794,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10922,7 +10922,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11050,7 +11050,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11178,7 +11178,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11306,7 +11306,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11434,7 +11434,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11562,7 +11562,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11818,7 +11818,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11946,7 +11946,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12202,7 +12202,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12330,7 +12330,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12458,7 +12458,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12586,7 +12586,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12842,7 +12842,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12970,7 +12970,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13098,7 +13098,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13226,7 +13226,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13354,7 +13354,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13482,7 +13482,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13610,7 +13610,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13738,7 +13738,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13866,7 +13866,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13994,7 +13994,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -14122,7 +14122,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -14250,7 +14250,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -14378,7 +14378,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -14506,7 +14506,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -14634,7 +14634,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -14762,7 +14762,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -14890,7 +14890,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15018,7 +15018,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15146,7 +15146,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15274,7 +15274,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15402,7 +15402,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15530,7 +15530,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15658,7 +15658,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15786,7 +15786,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15914,7 +15914,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -16042,7 +16042,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -16170,7 +16170,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -16298,7 +16298,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -16426,7 +16426,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -16682,7 +16682,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -16810,7 +16810,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -16938,7 +16938,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -17066,7 +17066,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -17194,7 +17194,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -17322,7 +17322,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -17450,7 +17450,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -17578,7 +17578,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -17706,7 +17706,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -17834,7 +17834,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -17962,7 +17962,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -18090,7 +18090,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -18218,7 +18218,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -18346,7 +18346,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -18474,7 +18474,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -18602,7 +18602,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -18730,7 +18730,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -18858,7 +18858,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -18986,7 +18986,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -19242,7 +19242,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -19370,7 +19370,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -19498,7 +19498,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -19626,7 +19626,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -19754,7 +19754,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -19882,7 +19882,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -20010,7 +20010,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -20138,7 +20138,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -20266,7 +20266,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -20394,7 +20394,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -20522,7 +20522,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -20778,7 +20778,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -20906,7 +20906,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -21162,7 +21162,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -21290,7 +21290,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -21418,7 +21418,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -21546,7 +21546,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -21674,7 +21674,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -21802,7 +21802,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -21930,7 +21930,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -22058,7 +22058,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -22186,7 +22186,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -22314,7 +22314,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -22442,7 +22442,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -22570,7 +22570,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -22698,7 +22698,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>

--- a/site/exports/Texas_Surplus_Feed.xlsx
+++ b/site/exports/Texas_Surplus_Feed.xlsx
@@ -682,7 +682,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -2602,7 +2602,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -3498,7 +3498,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -3754,7 +3754,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -4138,7 +4138,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -4266,7 +4266,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -4394,7 +4394,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -4522,7 +4522,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -4778,7 +4778,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -4906,7 +4906,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -5034,7 +5034,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -5162,7 +5162,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -5546,7 +5546,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -6698,7 +6698,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -7210,7 +7210,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -7466,7 +7466,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -7850,7 +7850,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -8106,7 +8106,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -8234,7 +8234,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -8362,7 +8362,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -8618,7 +8618,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -8746,7 +8746,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -9002,7 +9002,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -9130,7 +9130,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -9258,7 +9258,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -9386,7 +9386,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -9514,7 +9514,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -9642,7 +9642,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -9770,7 +9770,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -9898,7 +9898,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -10026,7 +10026,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -10154,7 +10154,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -10282,7 +10282,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -10410,7 +10410,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -10538,7 +10538,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -10666,7 +10666,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -10794,7 +10794,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -10922,7 +10922,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -11050,7 +11050,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -11178,7 +11178,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -11306,7 +11306,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -11434,7 +11434,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -11562,7 +11562,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -11818,7 +11818,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -11946,7 +11946,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -12202,7 +12202,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -12330,7 +12330,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -12458,7 +12458,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -12586,7 +12586,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -12842,7 +12842,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -12970,7 +12970,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -13098,7 +13098,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -13226,7 +13226,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -13354,7 +13354,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -13482,7 +13482,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -13610,7 +13610,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -13738,7 +13738,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -13866,7 +13866,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -13994,7 +13994,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -14122,7 +14122,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -14250,7 +14250,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -14378,7 +14378,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -14506,7 +14506,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -14634,7 +14634,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -14762,7 +14762,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -14890,7 +14890,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -15018,7 +15018,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -15146,7 +15146,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -15274,7 +15274,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -15402,7 +15402,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -15530,7 +15530,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -15658,7 +15658,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -15786,7 +15786,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -15914,7 +15914,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -16042,7 +16042,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -16170,7 +16170,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -16298,7 +16298,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -16426,7 +16426,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -16682,7 +16682,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -16810,7 +16810,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -16938,7 +16938,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -17066,7 +17066,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -17194,7 +17194,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -17322,7 +17322,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -17450,7 +17450,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -17578,7 +17578,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -17706,7 +17706,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -17834,7 +17834,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -17962,7 +17962,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -18090,7 +18090,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -18218,7 +18218,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -18346,7 +18346,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -18474,7 +18474,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -18602,7 +18602,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -18730,7 +18730,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -18858,7 +18858,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -18986,7 +18986,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -19242,7 +19242,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -19370,7 +19370,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -19498,7 +19498,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -19626,7 +19626,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -19754,7 +19754,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -19882,7 +19882,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -20010,7 +20010,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -20138,7 +20138,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -20266,7 +20266,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -20394,7 +20394,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -20522,7 +20522,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -20778,7 +20778,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -20906,7 +20906,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -21162,7 +21162,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -21290,7 +21290,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -21418,7 +21418,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -21546,7 +21546,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -21674,7 +21674,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -21802,7 +21802,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -21930,7 +21930,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -22058,7 +22058,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -22186,7 +22186,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -22314,7 +22314,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -22442,7 +22442,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -22570,7 +22570,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -22698,7 +22698,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>

--- a/site/exports/Texas_Surplus_Feed.xlsx
+++ b/site/exports/Texas_Surplus_Feed.xlsx
@@ -682,7 +682,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2602,7 +2602,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3498,7 +3498,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3754,7 +3754,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -4138,7 +4138,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -4266,7 +4266,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -4394,7 +4394,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -4522,7 +4522,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -4778,7 +4778,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -4906,7 +4906,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -5034,7 +5034,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -5162,7 +5162,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -5546,7 +5546,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -6698,7 +6698,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -7210,7 +7210,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -7466,7 +7466,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -7850,7 +7850,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -8106,7 +8106,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -8234,7 +8234,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -8362,7 +8362,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -8618,7 +8618,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -8746,7 +8746,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -9002,7 +9002,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -9130,7 +9130,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -9258,7 +9258,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -9386,7 +9386,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -9514,7 +9514,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -9642,7 +9642,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -9770,7 +9770,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -9898,7 +9898,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -10026,7 +10026,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -10154,7 +10154,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -10282,7 +10282,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -10410,7 +10410,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -10538,7 +10538,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -10666,7 +10666,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -10794,7 +10794,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -10922,7 +10922,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -11050,7 +11050,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -11178,7 +11178,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -11306,7 +11306,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -11434,7 +11434,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -11562,7 +11562,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -11818,7 +11818,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -11946,7 +11946,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -12202,7 +12202,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -12330,7 +12330,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -12458,7 +12458,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -12586,7 +12586,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -12842,7 +12842,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -12970,7 +12970,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -13098,7 +13098,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -13226,7 +13226,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -13354,7 +13354,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -13482,7 +13482,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -13610,7 +13610,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -13738,7 +13738,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -13866,7 +13866,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -13994,7 +13994,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -14122,7 +14122,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -14250,7 +14250,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -14378,7 +14378,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -14506,7 +14506,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -14634,7 +14634,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -14762,7 +14762,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -14890,7 +14890,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -15018,7 +15018,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -15146,7 +15146,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -15274,7 +15274,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -15402,7 +15402,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -15530,7 +15530,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -15658,7 +15658,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -15786,7 +15786,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -15914,7 +15914,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -16042,7 +16042,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -16170,7 +16170,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -16298,7 +16298,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -16426,7 +16426,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -16682,7 +16682,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -16810,7 +16810,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -16938,7 +16938,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -17066,7 +17066,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -17194,7 +17194,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -17322,7 +17322,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -17450,7 +17450,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -17578,7 +17578,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -17706,7 +17706,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -17834,7 +17834,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -17962,7 +17962,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -18090,7 +18090,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -18218,7 +18218,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -18346,7 +18346,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -18474,7 +18474,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -18602,7 +18602,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -18730,7 +18730,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -18858,7 +18858,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -18986,7 +18986,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -19242,7 +19242,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -19370,7 +19370,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -19498,7 +19498,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -19626,7 +19626,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -19754,7 +19754,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -19882,7 +19882,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -20010,7 +20010,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -20138,7 +20138,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -20266,7 +20266,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -20394,7 +20394,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -20522,7 +20522,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -20778,7 +20778,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -20906,7 +20906,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -21162,7 +21162,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -21290,7 +21290,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -21418,7 +21418,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -21546,7 +21546,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -21674,7 +21674,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -21802,7 +21802,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -21930,7 +21930,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -22058,7 +22058,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -22186,7 +22186,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -22314,7 +22314,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -22442,7 +22442,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -22570,7 +22570,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -22698,7 +22698,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>

--- a/site/exports/Texas_Surplus_Feed.xlsx
+++ b/site/exports/Texas_Surplus_Feed.xlsx
@@ -609,7 +609,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>P. &amp; B. K████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>P. &amp; B. A██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -664,7 +664,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -709,17 +709,17 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>P. &amp; B. K████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>P. &amp; B. A██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>K. &amp; A. H███████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>L. &amp; L. A██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -808,7 +808,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -853,17 +853,17 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>K. &amp; A. H███████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>L. &amp; L. A██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Y. &amp; M. L████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>R. &amp; V. W██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -952,7 +952,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -997,17 +997,17 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Y. &amp; M. L████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>R. &amp; V. W██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1231,7 +1231,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1285,12 +1285,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1573,12 +1573,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1717,12 +1717,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1861,12 +1861,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -2005,12 +2005,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>A. &amp; F. F██████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>P. &amp; B. H███████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -2149,17 +2149,17 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>A. &amp; F. F██████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>P. &amp; B. H███████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -2239,7 +2239,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2293,12 +2293,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2383,7 +2383,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2581,12 +2581,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2725,12 +2725,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2869,12 +2869,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>J. &amp; C. J████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>G. &amp; C. T█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -3157,17 +3157,17 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>J. &amp; C. J████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>G. &amp; C. T█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -3247,7 +3247,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -3301,12 +3301,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3391,7 +3391,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3445,12 +3445,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P22" t="n">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3679,7 +3679,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3733,12 +3733,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P24" t="n">
@@ -3832,7 +3832,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3877,12 +3877,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3967,7 +3967,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -4021,12 +4021,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -4065,7 +4065,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>A. &amp; E. P████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>R. &amp; D. P████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P26" t="n">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -4165,17 +4165,17 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>A. &amp; E. P████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>R. &amp; D. P████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -4255,7 +4255,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4399,7 +4399,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4453,12 +4453,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P29" t="n">
@@ -4552,7 +4552,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4831,7 +4831,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4885,12 +4885,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4975,7 +4975,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -5119,7 +5119,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P34" t="n">
@@ -5272,7 +5272,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>L. &amp; G. P████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>M. &amp; S. P████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P35" t="n">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -5461,17 +5461,17 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>L. &amp; G. P████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>M. &amp; S. P████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr">
@@ -5551,7 +5551,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -5605,12 +5605,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -5695,7 +5695,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -5749,12 +5749,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -5839,7 +5839,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -5893,12 +5893,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -5979,7 +5979,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P39" t="n">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -6181,12 +6181,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -6271,7 +6271,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -6325,12 +6325,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -6469,12 +6469,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -6559,7 +6559,7 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
@@ -6613,12 +6613,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -6703,7 +6703,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -6757,12 +6757,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -6847,7 +6847,7 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
@@ -6901,12 +6901,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -6987,7 +6987,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P46" t="n">
@@ -7000,7 +7000,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -7131,7 +7131,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P47" t="n">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -7423,7 +7423,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -7477,12 +7477,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -7567,7 +7567,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -7621,12 +7621,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -7707,7 +7707,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P51" t="n">
@@ -7720,7 +7720,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -7855,7 +7855,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -7909,12 +7909,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -7999,7 +7999,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -8053,12 +8053,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -8143,7 +8143,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -8197,12 +8197,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -8287,7 +8287,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -8341,12 +8341,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -8427,7 +8427,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P56" t="n">
@@ -8440,7 +8440,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -8485,12 +8485,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P57" t="n">
@@ -8584,7 +8584,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -8719,7 +8719,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -8773,12 +8773,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -8917,12 +8917,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
@@ -9003,7 +9003,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P60" t="n">
@@ -9016,7 +9016,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -9061,12 +9061,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
@@ -9151,7 +9151,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
@@ -9295,7 +9295,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -9349,12 +9349,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
@@ -9435,7 +9435,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P63" t="n">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -9493,12 +9493,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
@@ -9583,7 +9583,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
@@ -9727,7 +9727,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -9781,12 +9781,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
@@ -9871,7 +9871,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -9925,12 +9925,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
@@ -10011,7 +10011,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P67" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -10069,12 +10069,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
@@ -10159,7 +10159,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -10213,12 +10213,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
@@ -10299,7 +10299,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P69" t="n">
@@ -10312,7 +10312,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -10357,12 +10357,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
@@ -10447,7 +10447,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -10501,12 +10501,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
@@ -10587,7 +10587,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P71" t="n">
@@ -10600,7 +10600,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
@@ -10645,12 +10645,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
@@ -10735,7 +10735,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -10789,12 +10789,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
@@ -10879,7 +10879,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -10933,12 +10933,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
@@ -11023,7 +11023,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -11077,12 +11077,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
@@ -11167,7 +11167,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -11221,12 +11221,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
@@ -11307,7 +11307,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P76" t="n">
@@ -11320,7 +11320,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -11365,12 +11365,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
@@ -11451,7 +11451,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P77" t="n">
@@ -11464,7 +11464,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -11509,12 +11509,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
@@ -11599,7 +11599,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -11653,12 +11653,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
@@ -11743,7 +11743,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -11797,12 +11797,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
@@ -11887,7 +11887,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -11941,12 +11941,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
@@ -12031,7 +12031,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -12085,12 +12085,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
@@ -12175,7 +12175,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -12229,12 +12229,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
@@ -12319,7 +12319,7 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
@@ -12373,12 +12373,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
@@ -12459,7 +12459,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P84" t="n">
@@ -12472,7 +12472,7 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
@@ -12517,12 +12517,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
@@ -12607,7 +12607,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -12661,12 +12661,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
@@ -12747,7 +12747,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P86" t="n">
@@ -12760,7 +12760,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
@@ -12805,12 +12805,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
@@ -12895,7 +12895,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -12949,12 +12949,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
@@ -13035,7 +13035,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P88" t="n">
@@ -13048,7 +13048,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
@@ -13093,12 +13093,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
@@ -13179,7 +13179,7 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P89" t="n">
@@ -13192,7 +13192,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
@@ -13237,12 +13237,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
@@ -13323,7 +13323,7 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P90" t="n">
@@ -13336,7 +13336,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
@@ -13381,12 +13381,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
@@ -13471,7 +13471,7 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -13525,12 +13525,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
@@ -13611,7 +13611,7 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P92" t="n">
@@ -13624,7 +13624,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -13669,12 +13669,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>R. &amp; D. T█████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>D. &amp; W. H█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P93" t="n">
@@ -13768,7 +13768,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
@@ -13813,17 +13813,17 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>R. &amp; D. T█████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>D. &amp; W. H█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD93" t="inlineStr">
@@ -13899,7 +13899,7 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P94" t="n">
@@ -13912,7 +13912,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
@@ -13957,12 +13957,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
@@ -14043,7 +14043,7 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P95" t="n">
@@ -14056,7 +14056,7 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
@@ -14101,12 +14101,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
@@ -14191,7 +14191,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -14245,12 +14245,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
@@ -14335,7 +14335,7 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -14389,12 +14389,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
@@ -14479,7 +14479,7 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -14533,12 +14533,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
@@ -14623,7 +14623,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -14677,12 +14677,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
@@ -14763,7 +14763,7 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P100" t="n">
@@ -14776,7 +14776,7 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
@@ -14821,12 +14821,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
@@ -14865,7 +14865,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>S. &amp; W. W████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>J. &amp; L. A███████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -14907,7 +14907,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P101" t="n">
@@ -14920,7 +14920,7 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
@@ -14965,17 +14965,17 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>S. &amp; W. W████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>J. &amp; L. A███████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD101" t="inlineStr">
@@ -15051,7 +15051,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P102" t="n">
@@ -15064,7 +15064,7 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
@@ -15109,12 +15109,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
@@ -15199,7 +15199,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -15253,12 +15253,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
@@ -15339,7 +15339,7 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P104" t="n">
@@ -15352,7 +15352,7 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
@@ -15397,12 +15397,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
@@ -15487,7 +15487,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -15541,12 +15541,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
@@ -15631,7 +15631,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -15685,12 +15685,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
@@ -15771,7 +15771,7 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P107" t="n">
@@ -15784,7 +15784,7 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
@@ -15829,12 +15829,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
@@ -15915,7 +15915,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P108" t="n">
@@ -15928,7 +15928,7 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
@@ -15973,12 +15973,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC108" t="inlineStr">
@@ -16063,7 +16063,7 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -16117,12 +16117,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr">
@@ -16203,7 +16203,7 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P110" t="n">
@@ -16216,7 +16216,7 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S110" t="inlineStr">
@@ -16261,12 +16261,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr">
@@ -16347,7 +16347,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P111" t="n">
@@ -16360,7 +16360,7 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S111" t="inlineStr">
@@ -16405,12 +16405,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr">
@@ -16495,7 +16495,7 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -16549,12 +16549,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC112" t="inlineStr">
@@ -16635,7 +16635,7 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P113" t="n">
@@ -16648,7 +16648,7 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S113" t="inlineStr">
@@ -16693,12 +16693,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr">
@@ -16779,7 +16779,7 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P114" t="n">
@@ -16792,7 +16792,7 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S114" t="inlineStr">
@@ -16837,12 +16837,12 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr">
@@ -16927,7 +16927,7 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -16981,12 +16981,12 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr">
@@ -17071,7 +17071,7 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -17125,12 +17125,12 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr">
@@ -17215,7 +17215,7 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -17269,12 +17269,12 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
@@ -17359,7 +17359,7 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -17413,12 +17413,12 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC118" t="inlineStr">
@@ -17503,7 +17503,7 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -17557,12 +17557,12 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC119" t="inlineStr">
@@ -17643,7 +17643,7 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P120" t="n">
@@ -17656,7 +17656,7 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
@@ -17701,12 +17701,12 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC120" t="inlineStr">
@@ -17787,7 +17787,7 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P121" t="n">
@@ -17800,7 +17800,7 @@
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S121" t="inlineStr">
@@ -17845,12 +17845,12 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC121" t="inlineStr">
@@ -17935,7 +17935,7 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
@@ -17989,12 +17989,12 @@
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC122" t="inlineStr">
@@ -18079,7 +18079,7 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
@@ -18133,12 +18133,12 @@
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC123" t="inlineStr">
@@ -18177,7 +18177,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>C. &amp; G. B█████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>K. &amp; G. G█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -18219,7 +18219,7 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P124" t="n">
@@ -18232,7 +18232,7 @@
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S124" t="inlineStr">
@@ -18277,17 +18277,17 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>C. &amp; G. B█████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>K. &amp; G. G█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD124" t="inlineStr">
@@ -18367,7 +18367,7 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -18421,12 +18421,12 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC125" t="inlineStr">
@@ -18511,7 +18511,7 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
@@ -18565,12 +18565,12 @@
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC126" t="inlineStr">
@@ -18655,7 +18655,7 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
@@ -18709,12 +18709,12 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC127" t="inlineStr">
@@ -18753,7 +18753,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>G. &amp; S. S██████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>H. &amp; S. S██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -18795,7 +18795,7 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P128" t="n">
@@ -18808,7 +18808,7 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S128" t="inlineStr">
@@ -18853,17 +18853,17 @@
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>G. &amp; S. S██████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>H. &amp; S. S██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD128" t="inlineStr">
@@ -18897,7 +18897,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>A. &amp; A. M███████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>R. &amp; S. M████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -18939,7 +18939,7 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P129" t="n">
@@ -18952,7 +18952,7 @@
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S129" t="inlineStr">
@@ -18997,17 +18997,17 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>A. &amp; A. M███████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>R. &amp; S. M████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD129" t="inlineStr">
@@ -19087,7 +19087,7 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -19141,12 +19141,12 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC130" t="inlineStr">
@@ -19185,7 +19185,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>L. &amp; S. R██████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>R. &amp; R. R██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -19227,7 +19227,7 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P131" t="n">
@@ -19240,7 +19240,7 @@
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S131" t="inlineStr">
@@ -19285,17 +19285,17 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>L. &amp; S. R██████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>R. &amp; R. R██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD131" t="inlineStr">
@@ -19329,7 +19329,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>C. &amp; V. A███████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>C. &amp; V. C████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -19371,7 +19371,7 @@
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P132" t="n">
@@ -19384,7 +19384,7 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S132" t="inlineStr">
@@ -19429,17 +19429,17 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>C. &amp; V. A███████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>C. &amp; V. C████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD132" t="inlineStr">
@@ -19515,7 +19515,7 @@
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P133" t="n">
@@ -19528,7 +19528,7 @@
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S133" t="inlineStr">
@@ -19573,12 +19573,12 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC133" t="inlineStr">
@@ -19663,7 +19663,7 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
@@ -19717,12 +19717,12 @@
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC134" t="inlineStr">
@@ -19807,7 +19807,7 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
@@ -19861,12 +19861,12 @@
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC135" t="inlineStr">
@@ -19951,7 +19951,7 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
@@ -20005,12 +20005,12 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC136" t="inlineStr">
@@ -20095,7 +20095,7 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
@@ -20149,12 +20149,12 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC137" t="inlineStr">
@@ -20235,7 +20235,7 @@
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P138" t="n">
@@ -20248,7 +20248,7 @@
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S138" t="inlineStr">
@@ -20293,12 +20293,12 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC138" t="inlineStr">
@@ -20379,7 +20379,7 @@
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P139" t="n">
@@ -20392,7 +20392,7 @@
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S139" t="inlineStr">
@@ -20437,12 +20437,12 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC139" t="inlineStr">
@@ -20481,7 +20481,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>D. &amp; W. B██████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>E. &amp; B. B██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -20523,7 +20523,7 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P140" t="n">
@@ -20536,7 +20536,7 @@
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S140" t="inlineStr">
@@ -20581,17 +20581,17 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>D. &amp; W. B██████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>E. &amp; B. B██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD140" t="inlineStr">
@@ -20667,7 +20667,7 @@
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P141" t="n">
@@ -20680,7 +20680,7 @@
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S141" t="inlineStr">
@@ -20725,12 +20725,12 @@
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC141" t="inlineStr">
@@ -20811,7 +20811,7 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P142" t="n">
@@ -20824,7 +20824,7 @@
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S142" t="inlineStr">
@@ -20869,12 +20869,12 @@
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC142" t="inlineStr">
@@ -20955,7 +20955,7 @@
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P143" t="n">
@@ -20968,7 +20968,7 @@
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S143" t="inlineStr">
@@ -21013,12 +21013,12 @@
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC143" t="inlineStr">
@@ -21099,7 +21099,7 @@
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P144" t="n">
@@ -21112,7 +21112,7 @@
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S144" t="inlineStr">
@@ -21157,12 +21157,12 @@
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC144" t="inlineStr">
@@ -21247,7 +21247,7 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q145" t="inlineStr">
         <is>
@@ -21301,12 +21301,12 @@
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC145" t="inlineStr">
@@ -21391,7 +21391,7 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q146" t="inlineStr">
         <is>
@@ -21445,12 +21445,12 @@
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC146" t="inlineStr">
@@ -21531,7 +21531,7 @@
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P147" t="n">
@@ -21544,7 +21544,7 @@
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S147" t="inlineStr">
@@ -21589,12 +21589,12 @@
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC147" t="inlineStr">
@@ -21679,7 +21679,7 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="Q148" t="inlineStr">
         <is>
@@ -21733,12 +21733,12 @@
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC148" t="inlineStr">
@@ -21823,7 +21823,7 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q149" t="inlineStr">
         <is>
@@ -21877,12 +21877,12 @@
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC149" t="inlineStr">
@@ -21967,7 +21967,7 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="Q150" t="inlineStr">
         <is>
@@ -22021,12 +22021,12 @@
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC150" t="inlineStr">
@@ -22107,7 +22107,7 @@
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P151" t="n">
@@ -22120,7 +22120,7 @@
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S151" t="inlineStr">
@@ -22165,12 +22165,12 @@
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC151" t="inlineStr">
@@ -22255,7 +22255,7 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q152" t="inlineStr">
         <is>
@@ -22309,12 +22309,12 @@
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC152" t="inlineStr">
@@ -22395,7 +22395,7 @@
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P153" t="n">
@@ -22408,7 +22408,7 @@
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S153" t="inlineStr">
@@ -22453,12 +22453,12 @@
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC153" t="inlineStr">
@@ -22543,7 +22543,7 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q154" t="inlineStr">
         <is>
@@ -22597,12 +22597,12 @@
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC154" t="inlineStr">
@@ -22683,7 +22683,7 @@
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P155" t="n">
@@ -22696,7 +22696,7 @@
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S155" t="inlineStr">
@@ -22741,12 +22741,12 @@
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC155" t="inlineStr">
@@ -22827,7 +22827,7 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P156" t="n">
@@ -22840,7 +22840,7 @@
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S156" t="inlineStr">
@@ -22885,12 +22885,12 @@
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC156" t="inlineStr">
@@ -22975,7 +22975,7 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q157" t="inlineStr">
         <is>
@@ -23029,12 +23029,12 @@
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC157" t="inlineStr">
@@ -23119,7 +23119,7 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q158" t="inlineStr">
         <is>
@@ -23173,12 +23173,12 @@
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC158" t="inlineStr">
@@ -23217,7 +23217,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>V. &amp; W. L████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>M. &amp; A. G████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -23259,7 +23259,7 @@
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P159" t="n">
@@ -23272,7 +23272,7 @@
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S159" t="inlineStr">
@@ -23317,17 +23317,17 @@
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC159" t="inlineStr">
         <is>
-          <t>V. &amp; W. L████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>M. &amp; A. G████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD159" t="inlineStr">
@@ -23407,7 +23407,7 @@
         </is>
       </c>
       <c r="P160" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q160" t="inlineStr">
         <is>
@@ -23461,12 +23461,12 @@
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC160" t="inlineStr">
@@ -23551,7 +23551,7 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q161" t="inlineStr">
         <is>
@@ -23605,12 +23605,12 @@
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC161" t="inlineStr">
@@ -23691,7 +23691,7 @@
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P162" t="n">
@@ -23704,7 +23704,7 @@
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S162" t="inlineStr">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC162" t="inlineStr">
@@ -23839,7 +23839,7 @@
         </is>
       </c>
       <c r="P163" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q163" t="inlineStr">
         <is>
@@ -23893,12 +23893,12 @@
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC163" t="inlineStr">
@@ -23983,7 +23983,7 @@
         </is>
       </c>
       <c r="P164" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q164" t="inlineStr">
         <is>
@@ -24037,12 +24037,12 @@
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC164" t="inlineStr">
@@ -24127,7 +24127,7 @@
         </is>
       </c>
       <c r="P165" t="n">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q165" t="inlineStr">
         <is>
@@ -24181,12 +24181,12 @@
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC165" t="inlineStr">
@@ -24267,7 +24267,7 @@
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P166" t="n">
@@ -24280,7 +24280,7 @@
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>2028-10-25</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="S166" t="inlineStr">
@@ -24325,12 +24325,12 @@
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:09Z</t>
+          <t>2026-10-27T09:47:08Z</t>
         </is>
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC166" t="inlineStr">
@@ -24415,7 +24415,7 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="Q167" t="inlineStr">
         <is>
@@ -24469,12 +24469,12 @@
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC167" t="inlineStr">
@@ -24559,7 +24559,7 @@
         </is>
       </c>
       <c r="P168" t="n">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="Q168" t="inlineStr">
         <is>
@@ -24613,12 +24613,12 @@
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC168" t="inlineStr">
@@ -24703,7 +24703,7 @@
         </is>
       </c>
       <c r="P169" t="n">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="Q169" t="inlineStr">
         <is>
@@ -24757,12 +24757,12 @@
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC169" t="inlineStr">
@@ -24847,7 +24847,7 @@
         </is>
       </c>
       <c r="P170" t="n">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="Q170" t="inlineStr">
         <is>
@@ -24901,12 +24901,12 @@
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC170" t="inlineStr">
@@ -24991,7 +24991,7 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="Q171" t="inlineStr">
         <is>
@@ -25045,12 +25045,12 @@
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC171" t="inlineStr">
@@ -25135,7 +25135,7 @@
         </is>
       </c>
       <c r="P172" t="n">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="Q172" t="inlineStr">
         <is>
@@ -25189,12 +25189,12 @@
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:08Z</t>
+          <t>2026-10-27T09:47:07Z</t>
         </is>
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC172" t="inlineStr">

--- a/site/exports/Texas_Surplus_Feed.xlsx
+++ b/site/exports/Texas_Surplus_Feed.xlsx
@@ -609,7 +609,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>P. &amp; B. A██████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>P. &amp; B. K████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -664,7 +664,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -709,17 +709,17 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>P. &amp; B. A██████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>P. &amp; B. K████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -808,7 +808,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -853,12 +853,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -952,7 +952,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -997,12 +997,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>J. &amp; W. S███████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>J. &amp; C. S██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1141,17 +1141,17 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>J. &amp; W. S███████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>J. &amp; C. S██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -1231,7 +1231,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1285,12 +1285,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>C. &amp; F. S████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>R. &amp; R. C████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>C. &amp; F. S████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>R. &amp; R. C████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1573,12 +1573,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>S. &amp; F. C█████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>I. &amp; R. A███████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1717,17 +1717,17 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>S. &amp; F. C█████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>I. &amp; R. A███████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1861,12 +1861,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -2005,12 +2005,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2239,7 +2239,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2293,12 +2293,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2383,7 +2383,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2581,12 +2581,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2725,12 +2725,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2869,12 +2869,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3247,7 +3247,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -3301,12 +3301,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3391,7 +3391,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3445,12 +3445,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P22" t="n">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3679,7 +3679,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3733,12 +3733,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Y. &amp; M. C█████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>B. &amp; K. C█████████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P24" t="n">
@@ -3832,7 +3832,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3877,17 +3877,17 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Y. &amp; M. C█████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>B. &amp; K. C█████████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -3967,7 +3967,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -4021,12 +4021,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P26" t="n">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -4255,7 +4255,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4399,7 +4399,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4453,12 +4453,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P29" t="n">
@@ -4552,7 +4552,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4831,7 +4831,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4885,12 +4885,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4975,7 +4975,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -5119,7 +5119,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P34" t="n">
@@ -5272,7 +5272,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P35" t="n">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -5551,7 +5551,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -5605,12 +5605,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -5695,7 +5695,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -5749,12 +5749,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -5839,7 +5839,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -5893,12 +5893,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -5979,7 +5979,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P39" t="n">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -6181,12 +6181,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -6271,7 +6271,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -6325,12 +6325,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -6469,12 +6469,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -6559,7 +6559,7 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
@@ -6613,12 +6613,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -6703,7 +6703,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -6757,12 +6757,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -6847,7 +6847,7 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
@@ -6901,12 +6901,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -6987,7 +6987,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P46" t="n">
@@ -7000,7 +7000,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -7131,7 +7131,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P47" t="n">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -7423,7 +7423,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -7477,12 +7477,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -7567,7 +7567,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -7621,12 +7621,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -7707,7 +7707,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P51" t="n">
@@ -7720,7 +7720,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -7855,7 +7855,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -7909,12 +7909,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -7999,7 +7999,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -8053,12 +8053,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -8143,7 +8143,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -8197,12 +8197,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -8287,7 +8287,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -8341,12 +8341,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -8427,7 +8427,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P56" t="n">
@@ -8440,7 +8440,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -8485,12 +8485,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P57" t="n">
@@ -8584,7 +8584,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -8719,7 +8719,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -8773,12 +8773,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -8917,12 +8917,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
@@ -9003,7 +9003,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P60" t="n">
@@ -9016,7 +9016,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -9061,12 +9061,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
@@ -9151,7 +9151,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
@@ -9295,7 +9295,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -9349,12 +9349,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
@@ -9435,7 +9435,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P63" t="n">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -9493,12 +9493,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
@@ -9583,7 +9583,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
@@ -9727,7 +9727,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -9781,12 +9781,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
@@ -9871,7 +9871,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -9925,12 +9925,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
@@ -10011,7 +10011,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P67" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -10069,12 +10069,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
@@ -10159,7 +10159,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -10213,12 +10213,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
@@ -10299,7 +10299,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P69" t="n">
@@ -10312,7 +10312,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -10357,12 +10357,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
@@ -10447,7 +10447,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -10501,12 +10501,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
@@ -10587,7 +10587,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P71" t="n">
@@ -10600,7 +10600,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
@@ -10645,12 +10645,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
@@ -10735,7 +10735,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -10789,12 +10789,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
@@ -10879,7 +10879,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -10933,12 +10933,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
@@ -11023,7 +11023,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -11077,12 +11077,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
@@ -11167,7 +11167,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -11221,12 +11221,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
@@ -11307,7 +11307,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P76" t="n">
@@ -11320,7 +11320,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -11365,12 +11365,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
@@ -11451,7 +11451,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P77" t="n">
@@ -11464,7 +11464,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -11509,12 +11509,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
@@ -11599,7 +11599,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -11653,12 +11653,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
@@ -11743,7 +11743,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -11797,12 +11797,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
@@ -11887,7 +11887,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -11941,12 +11941,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
@@ -12031,7 +12031,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -12085,12 +12085,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
@@ -12175,7 +12175,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -12229,12 +12229,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
@@ -12319,7 +12319,7 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
@@ -12373,12 +12373,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
@@ -12417,7 +12417,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>L. &amp; M. L████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>L. &amp; G. J████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -12459,7 +12459,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P84" t="n">
@@ -12472,7 +12472,7 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
@@ -12517,17 +12517,17 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>L. &amp; M. L████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>L. &amp; G. J████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD84" t="inlineStr">
@@ -12607,7 +12607,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -12661,12 +12661,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
@@ -12747,7 +12747,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P86" t="n">
@@ -12760,7 +12760,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
@@ -12805,12 +12805,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
@@ -12895,7 +12895,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -12949,12 +12949,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
@@ -13035,7 +13035,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P88" t="n">
@@ -13048,7 +13048,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
@@ -13093,12 +13093,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
@@ -13179,7 +13179,7 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P89" t="n">
@@ -13192,7 +13192,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
@@ -13237,12 +13237,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
@@ -13323,7 +13323,7 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P90" t="n">
@@ -13336,7 +13336,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
@@ -13381,12 +13381,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
@@ -13471,7 +13471,7 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -13525,12 +13525,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
@@ -13611,7 +13611,7 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P92" t="n">
@@ -13624,7 +13624,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -13669,12 +13669,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>D. &amp; W. H█████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>M. &amp; J. J████████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P93" t="n">
@@ -13768,7 +13768,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
@@ -13813,17 +13813,17 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>D. &amp; W. H█████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>M. &amp; J. J████████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD93" t="inlineStr">
@@ -13899,7 +13899,7 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P94" t="n">
@@ -13912,7 +13912,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
@@ -13957,12 +13957,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
@@ -14043,7 +14043,7 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P95" t="n">
@@ -14056,7 +14056,7 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
@@ -14101,12 +14101,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
@@ -14191,7 +14191,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -14245,12 +14245,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
@@ -14335,7 +14335,7 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -14389,12 +14389,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
@@ -14479,7 +14479,7 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -14533,12 +14533,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
@@ -14623,7 +14623,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -14677,12 +14677,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
@@ -14721,7 +14721,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>J. &amp; D. S████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>S. &amp; D. D██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -14763,7 +14763,7 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P100" t="n">
@@ -14776,7 +14776,7 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
@@ -14821,17 +14821,17 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>J. &amp; D. S████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>S. &amp; D. D██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD100" t="inlineStr">
@@ -14865,7 +14865,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>J. &amp; L. A███████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>S. &amp; W. W████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -14907,7 +14907,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P101" t="n">
@@ -14920,7 +14920,7 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
@@ -14965,17 +14965,17 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>J. &amp; L. A███████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>S. &amp; W. W████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD101" t="inlineStr">
@@ -15051,7 +15051,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P102" t="n">
@@ -15064,7 +15064,7 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
@@ -15109,12 +15109,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
@@ -15199,7 +15199,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -15253,12 +15253,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
@@ -15339,7 +15339,7 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P104" t="n">
@@ -15352,7 +15352,7 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
@@ -15397,12 +15397,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
@@ -15487,7 +15487,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -15541,12 +15541,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
@@ -15631,7 +15631,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -15685,12 +15685,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
@@ -15771,7 +15771,7 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P107" t="n">
@@ -15784,7 +15784,7 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
@@ -15829,12 +15829,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
@@ -15915,7 +15915,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P108" t="n">
@@ -15928,7 +15928,7 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
@@ -15973,12 +15973,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC108" t="inlineStr">
@@ -16063,7 +16063,7 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -16117,12 +16117,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr">
@@ -16203,7 +16203,7 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P110" t="n">
@@ -16216,7 +16216,7 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S110" t="inlineStr">
@@ -16261,12 +16261,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr">
@@ -16347,7 +16347,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P111" t="n">
@@ -16360,7 +16360,7 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S111" t="inlineStr">
@@ -16405,12 +16405,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr">
@@ -16495,7 +16495,7 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -16549,12 +16549,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC112" t="inlineStr">
@@ -16635,7 +16635,7 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P113" t="n">
@@ -16648,7 +16648,7 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S113" t="inlineStr">
@@ -16693,12 +16693,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr">
@@ -16779,7 +16779,7 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P114" t="n">
@@ -16792,7 +16792,7 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S114" t="inlineStr">
@@ -16837,12 +16837,12 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr">
@@ -16927,7 +16927,7 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -16981,12 +16981,12 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr">
@@ -17071,7 +17071,7 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -17125,12 +17125,12 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr">
@@ -17215,7 +17215,7 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -17269,12 +17269,12 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
@@ -17359,7 +17359,7 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -17413,12 +17413,12 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC118" t="inlineStr">
@@ -17503,7 +17503,7 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -17557,12 +17557,12 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC119" t="inlineStr">
@@ -17643,7 +17643,7 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P120" t="n">
@@ -17656,7 +17656,7 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
@@ -17701,12 +17701,12 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC120" t="inlineStr">
@@ -17745,7 +17745,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>D. &amp; L. S██████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>E. &amp; N. S██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -17787,7 +17787,7 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P121" t="n">
@@ -17800,7 +17800,7 @@
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S121" t="inlineStr">
@@ -17845,17 +17845,17 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>D. &amp; L. S██████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>E. &amp; N. S██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD121" t="inlineStr">
@@ -17935,7 +17935,7 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
@@ -17989,12 +17989,12 @@
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC122" t="inlineStr">
@@ -18079,7 +18079,7 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
@@ -18133,12 +18133,12 @@
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC123" t="inlineStr">
@@ -18177,7 +18177,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>K. &amp; G. G█████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>F. &amp; G. T████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -18219,7 +18219,7 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P124" t="n">
@@ -18232,7 +18232,7 @@
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S124" t="inlineStr">
@@ -18277,17 +18277,17 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>K. &amp; G. G█████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>F. &amp; G. T████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD124" t="inlineStr">
@@ -18367,7 +18367,7 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -18421,12 +18421,12 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC125" t="inlineStr">
@@ -18511,7 +18511,7 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
@@ -18565,12 +18565,12 @@
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC126" t="inlineStr">
@@ -18655,7 +18655,7 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
@@ -18709,12 +18709,12 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC127" t="inlineStr">
@@ -18753,7 +18753,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>H. &amp; S. S██████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>D. &amp; S. S██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -18795,7 +18795,7 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P128" t="n">
@@ -18808,7 +18808,7 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S128" t="inlineStr">
@@ -18853,17 +18853,17 @@
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>H. &amp; S. S██████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>D. &amp; S. S██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD128" t="inlineStr">
@@ -18939,7 +18939,7 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P129" t="n">
@@ -18952,7 +18952,7 @@
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S129" t="inlineStr">
@@ -18997,12 +18997,12 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC129" t="inlineStr">
@@ -19087,7 +19087,7 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -19141,12 +19141,12 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC130" t="inlineStr">
@@ -19185,7 +19185,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>R. &amp; R. R██████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>K. &amp; R. N████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -19227,7 +19227,7 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P131" t="n">
@@ -19240,7 +19240,7 @@
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S131" t="inlineStr">
@@ -19285,17 +19285,17 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>R. &amp; R. R██████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>K. &amp; R. N████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD131" t="inlineStr">
@@ -19329,7 +19329,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>C. &amp; V. C████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>V. &amp; C. V███████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -19371,7 +19371,7 @@
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P132" t="n">
@@ -19384,7 +19384,7 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S132" t="inlineStr">
@@ -19429,17 +19429,17 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>C. &amp; V. C████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>V. &amp; C. V███████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD132" t="inlineStr">
@@ -19515,7 +19515,7 @@
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P133" t="n">
@@ -19528,7 +19528,7 @@
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S133" t="inlineStr">
@@ -19573,12 +19573,12 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC133" t="inlineStr">
@@ -19663,7 +19663,7 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
@@ -19717,12 +19717,12 @@
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC134" t="inlineStr">
@@ -19807,7 +19807,7 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
@@ -19861,12 +19861,12 @@
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC135" t="inlineStr">
@@ -19951,7 +19951,7 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
@@ -20005,12 +20005,12 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC136" t="inlineStr">
@@ -20095,7 +20095,7 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
@@ -20149,12 +20149,12 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC137" t="inlineStr">
@@ -20235,7 +20235,7 @@
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P138" t="n">
@@ -20248,7 +20248,7 @@
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S138" t="inlineStr">
@@ -20293,12 +20293,12 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC138" t="inlineStr">
@@ -20379,7 +20379,7 @@
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P139" t="n">
@@ -20392,7 +20392,7 @@
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S139" t="inlineStr">
@@ -20437,12 +20437,12 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC139" t="inlineStr">
@@ -20523,7 +20523,7 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P140" t="n">
@@ -20536,7 +20536,7 @@
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S140" t="inlineStr">
@@ -20581,12 +20581,12 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC140" t="inlineStr">
@@ -20667,7 +20667,7 @@
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P141" t="n">
@@ -20680,7 +20680,7 @@
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S141" t="inlineStr">
@@ -20725,12 +20725,12 @@
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC141" t="inlineStr">
@@ -20811,7 +20811,7 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P142" t="n">
@@ -20824,7 +20824,7 @@
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S142" t="inlineStr">
@@ -20869,12 +20869,12 @@
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC142" t="inlineStr">
@@ -20955,7 +20955,7 @@
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P143" t="n">
@@ -20968,7 +20968,7 @@
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S143" t="inlineStr">
@@ -21013,12 +21013,12 @@
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC143" t="inlineStr">
@@ -21099,7 +21099,7 @@
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P144" t="n">
@@ -21112,7 +21112,7 @@
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S144" t="inlineStr">
@@ -21157,12 +21157,12 @@
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC144" t="inlineStr">
@@ -21247,7 +21247,7 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="Q145" t="inlineStr">
         <is>
@@ -21301,12 +21301,12 @@
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC145" t="inlineStr">
@@ -21391,7 +21391,7 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q146" t="inlineStr">
         <is>
@@ -21445,12 +21445,12 @@
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC146" t="inlineStr">
@@ -21489,7 +21489,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>F. &amp; H. T████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>L. &amp; E. T████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -21531,7 +21531,7 @@
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P147" t="n">
@@ -21544,7 +21544,7 @@
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S147" t="inlineStr">
@@ -21589,17 +21589,17 @@
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>F. &amp; H. T████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>L. &amp; E. T████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD147" t="inlineStr">
@@ -21679,7 +21679,7 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="Q148" t="inlineStr">
         <is>
@@ -21733,12 +21733,12 @@
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC148" t="inlineStr">
@@ -21823,7 +21823,7 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="Q149" t="inlineStr">
         <is>
@@ -21877,12 +21877,12 @@
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC149" t="inlineStr">
@@ -21967,7 +21967,7 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Q150" t="inlineStr">
         <is>
@@ -22021,12 +22021,12 @@
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC150" t="inlineStr">
@@ -22065,7 +22065,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>L. &amp; G. D████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>D. &amp; M. D████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -22107,7 +22107,7 @@
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P151" t="n">
@@ -22120,7 +22120,7 @@
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S151" t="inlineStr">
@@ -22165,17 +22165,17 @@
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>L. &amp; G. D████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>D. &amp; M. D████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD151" t="inlineStr">
@@ -22255,7 +22255,7 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q152" t="inlineStr">
         <is>
@@ -22309,12 +22309,12 @@
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC152" t="inlineStr">
@@ -22395,7 +22395,7 @@
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P153" t="n">
@@ -22408,7 +22408,7 @@
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S153" t="inlineStr">
@@ -22453,12 +22453,12 @@
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC153" t="inlineStr">
@@ -22543,7 +22543,7 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q154" t="inlineStr">
         <is>
@@ -22597,12 +22597,12 @@
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC154" t="inlineStr">
@@ -22683,7 +22683,7 @@
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P155" t="n">
@@ -22696,7 +22696,7 @@
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S155" t="inlineStr">
@@ -22741,12 +22741,12 @@
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC155" t="inlineStr">
@@ -22827,7 +22827,7 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P156" t="n">
@@ -22840,7 +22840,7 @@
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S156" t="inlineStr">
@@ -22885,12 +22885,12 @@
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC156" t="inlineStr">
@@ -22975,7 +22975,7 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q157" t="inlineStr">
         <is>
@@ -23029,12 +23029,12 @@
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC157" t="inlineStr">
@@ -23119,7 +23119,7 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Q158" t="inlineStr">
         <is>
@@ -23173,12 +23173,12 @@
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC158" t="inlineStr">
@@ -23217,7 +23217,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>M. &amp; A. G████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>D. &amp; M. W███████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -23259,7 +23259,7 @@
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P159" t="n">
@@ -23272,7 +23272,7 @@
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S159" t="inlineStr">
@@ -23317,17 +23317,17 @@
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC159" t="inlineStr">
         <is>
-          <t>M. &amp; A. G████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>D. &amp; M. W███████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD159" t="inlineStr">
@@ -23407,7 +23407,7 @@
         </is>
       </c>
       <c r="P160" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q160" t="inlineStr">
         <is>
@@ -23461,12 +23461,12 @@
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC160" t="inlineStr">
@@ -23551,7 +23551,7 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q161" t="inlineStr">
         <is>
@@ -23605,12 +23605,12 @@
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC161" t="inlineStr">
@@ -23691,7 +23691,7 @@
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P162" t="n">
@@ -23704,7 +23704,7 @@
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S162" t="inlineStr">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC162" t="inlineStr">
@@ -23839,7 +23839,7 @@
         </is>
       </c>
       <c r="P163" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q163" t="inlineStr">
         <is>
@@ -23893,12 +23893,12 @@
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC163" t="inlineStr">
@@ -23983,7 +23983,7 @@
         </is>
       </c>
       <c r="P164" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q164" t="inlineStr">
         <is>
@@ -24037,12 +24037,12 @@
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC164" t="inlineStr">
@@ -24127,7 +24127,7 @@
         </is>
       </c>
       <c r="P165" t="n">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="Q165" t="inlineStr">
         <is>
@@ -24181,12 +24181,12 @@
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC165" t="inlineStr">
@@ -24267,7 +24267,7 @@
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P166" t="n">
@@ -24280,7 +24280,7 @@
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
+          <t>2028-10-27</t>
         </is>
       </c>
       <c r="S166" t="inlineStr">
@@ -24325,12 +24325,12 @@
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:08Z</t>
+          <t>2026-10-28T10:32:05Z</t>
         </is>
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC166" t="inlineStr">
@@ -24415,7 +24415,7 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="Q167" t="inlineStr">
         <is>
@@ -24469,12 +24469,12 @@
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC167" t="inlineStr">
@@ -24559,7 +24559,7 @@
         </is>
       </c>
       <c r="P168" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="Q168" t="inlineStr">
         <is>
@@ -24613,12 +24613,12 @@
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC168" t="inlineStr">
@@ -24703,7 +24703,7 @@
         </is>
       </c>
       <c r="P169" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="Q169" t="inlineStr">
         <is>
@@ -24757,12 +24757,12 @@
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC169" t="inlineStr">
@@ -24847,7 +24847,7 @@
         </is>
       </c>
       <c r="P170" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="Q170" t="inlineStr">
         <is>
@@ -24901,12 +24901,12 @@
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC170" t="inlineStr">
@@ -24991,7 +24991,7 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="Q171" t="inlineStr">
         <is>
@@ -25045,12 +25045,12 @@
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC171" t="inlineStr">
@@ -25135,7 +25135,7 @@
         </is>
       </c>
       <c r="P172" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="Q172" t="inlineStr">
         <is>
@@ -25189,12 +25189,12 @@
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:07Z</t>
+          <t>2026-10-28T10:32:04Z</t>
         </is>
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC172" t="inlineStr">

--- a/site/exports/Texas_Surplus_Feed.xlsx
+++ b/site/exports/Texas_Surplus_Feed.xlsx
@@ -609,7 +609,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>K. &amp; W. R█████████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>P. &amp; B. A██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -664,7 +664,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -709,17 +709,17 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>K. &amp; W. R█████████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>P. &amp; B. A██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -808,7 +808,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -853,12 +853,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -952,7 +952,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -997,12 +997,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>J. &amp; W. S██████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>J. &amp; W. S███████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1141,17 +1141,17 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>J. &amp; W. S██████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>J. &amp; W. S███████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -1231,7 +1231,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1285,12 +1285,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1573,12 +1573,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1717,12 +1717,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1861,12 +1861,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -2005,12 +2005,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2239,7 +2239,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2293,12 +2293,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2383,7 +2383,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2581,12 +2581,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2725,12 +2725,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2869,12 +2869,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>S. &amp; C. M███████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>G. &amp; C. T█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -3157,17 +3157,17 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>S. &amp; C. M███████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>G. &amp; C. T█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -3247,7 +3247,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -3301,12 +3301,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3391,7 +3391,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3445,12 +3445,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P22" t="n">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3679,7 +3679,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3733,12 +3733,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P24" t="n">
@@ -3832,7 +3832,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3877,12 +3877,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3967,7 +3967,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -4021,12 +4021,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -4111,7 +4111,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -4255,7 +4255,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4353,7 +4353,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>B. &amp; S. P███████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>G. &amp; K. K████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P28" t="n">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -4453,17 +4453,17 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>B. &amp; S. P███████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>G. &amp; K. K████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -4543,7 +4543,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4597,12 +4597,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4831,7 +4831,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4885,12 +4885,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4975,7 +4975,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -5115,7 +5115,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P33" t="n">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -5173,12 +5173,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P34" t="n">
@@ -5272,7 +5272,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -5407,7 +5407,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -5461,12 +5461,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -5551,7 +5551,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -5605,12 +5605,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -5695,7 +5695,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -5749,12 +5749,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -5835,7 +5835,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P38" t="n">
@@ -5848,7 +5848,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -5983,7 +5983,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -6037,12 +6037,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -6181,12 +6181,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -6271,7 +6271,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -6325,12 +6325,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -6469,12 +6469,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -6559,7 +6559,7 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
@@ -6613,12 +6613,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -6703,7 +6703,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -6757,12 +6757,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -6843,7 +6843,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P45" t="n">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -6901,12 +6901,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -6945,7 +6945,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>A. &amp; M. B██████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>M. &amp; J. M█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -6987,7 +6987,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P46" t="n">
@@ -7000,7 +7000,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -7045,17 +7045,17 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>A. &amp; M. B██████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>M. &amp; J. M█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD46" t="inlineStr">
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -7189,12 +7189,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -7423,7 +7423,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -7477,12 +7477,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P50" t="n">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -7621,12 +7621,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -7711,7 +7711,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -7765,12 +7765,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -7855,7 +7855,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -7909,12 +7909,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -7999,7 +7999,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -8053,12 +8053,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -8143,7 +8143,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -8197,12 +8197,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P55" t="n">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -8341,12 +8341,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -8427,7 +8427,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P56" t="n">
@@ -8440,7 +8440,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -8485,12 +8485,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
@@ -8575,7 +8575,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -8629,12 +8629,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -8719,7 +8719,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -8773,12 +8773,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P59" t="n">
@@ -8872,7 +8872,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -8917,12 +8917,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
@@ -9007,7 +9007,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -9061,12 +9061,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
@@ -9151,7 +9151,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
@@ -9291,7 +9291,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P62" t="n">
@@ -9304,7 +9304,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -9349,12 +9349,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
@@ -9439,7 +9439,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
@@ -9583,7 +9583,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
@@ -9727,7 +9727,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -9781,12 +9781,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
@@ -9825,7 +9825,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>M. &amp; L. D████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>D. &amp; A. D████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -9867,7 +9867,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P66" t="n">
@@ -9880,7 +9880,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -9925,17 +9925,17 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>M. &amp; L. D████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>D. &amp; A. D████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD66" t="inlineStr">
@@ -10015,7 +10015,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -10069,12 +10069,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
@@ -10155,7 +10155,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P68" t="n">
@@ -10168,7 +10168,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -10213,12 +10213,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
@@ -10303,7 +10303,7 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -10357,12 +10357,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P70" t="n">
@@ -10456,7 +10456,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
@@ -10591,7 +10591,7 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -10645,12 +10645,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
@@ -10735,7 +10735,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -10789,12 +10789,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
@@ -10879,7 +10879,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -10933,12 +10933,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
@@ -11023,7 +11023,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -11077,12 +11077,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
@@ -11163,7 +11163,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P75" t="n">
@@ -11176,7 +11176,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
@@ -11307,7 +11307,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P76" t="n">
@@ -11320,7 +11320,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -11365,12 +11365,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
@@ -11455,7 +11455,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -11509,12 +11509,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
@@ -11599,7 +11599,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -11653,12 +11653,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
@@ -11743,7 +11743,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -11797,12 +11797,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
@@ -11887,7 +11887,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -11941,12 +11941,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
@@ -12031,7 +12031,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -12085,12 +12085,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
@@ -12175,7 +12175,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -12229,12 +12229,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
@@ -12315,7 +12315,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P83" t="n">
@@ -12328,7 +12328,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
@@ -12463,7 +12463,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>-29</v>
+        <v>-30</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -12517,12 +12517,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
@@ -12603,7 +12603,7 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P85" t="n">
@@ -12616,7 +12616,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
@@ -12661,12 +12661,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
@@ -12751,7 +12751,7 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
@@ -12805,12 +12805,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
@@ -12849,7 +12849,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>L. &amp; G. W██████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>B. &amp; K. H███████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -12891,7 +12891,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P87" t="n">
@@ -12904,7 +12904,7 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
@@ -12949,17 +12949,17 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>L. &amp; G. W██████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>B. &amp; K. H███████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD87" t="inlineStr">
@@ -13035,7 +13035,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P88" t="n">
@@ -13048,7 +13048,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
@@ -13093,12 +13093,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
@@ -13183,7 +13183,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -13237,12 +13237,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
@@ -13323,7 +13323,7 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P90" t="n">
@@ -13336,7 +13336,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
@@ -13381,12 +13381,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
@@ -13425,7 +13425,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>M. &amp; J. J████████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>P. &amp; V. J████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -13467,7 +13467,7 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P91" t="n">
@@ -13480,7 +13480,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
@@ -13525,17 +13525,17 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>M. &amp; J. J████████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>P. &amp; V. J████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD91" t="inlineStr">
@@ -13611,7 +13611,7 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P92" t="n">
@@ -13624,7 +13624,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -13669,12 +13669,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P93" t="n">
@@ -13768,7 +13768,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
@@ -13813,12 +13813,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
@@ -13903,7 +13903,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -13957,12 +13957,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
@@ -14047,7 +14047,7 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -14101,12 +14101,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
@@ -14191,7 +14191,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -14245,12 +14245,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
@@ -14335,7 +14335,7 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -14389,12 +14389,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
@@ -14433,7 +14433,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>J. &amp; D. S████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>S. &amp; D. S████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -14475,7 +14475,7 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P98" t="n">
@@ -14488,7 +14488,7 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
@@ -14533,17 +14533,17 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>J. &amp; D. S████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>S. &amp; D. S████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD98" t="inlineStr">
@@ -14619,7 +14619,7 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P99" t="n">
@@ -14632,7 +14632,7 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
@@ -14677,12 +14677,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
@@ -14763,7 +14763,7 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P100" t="n">
@@ -14776,7 +14776,7 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
@@ -14821,12 +14821,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
@@ -14911,7 +14911,7 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -14965,12 +14965,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
@@ -15051,7 +15051,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P102" t="n">
@@ -15064,7 +15064,7 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
@@ -15109,12 +15109,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
@@ -15199,7 +15199,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -15253,12 +15253,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
@@ -15343,7 +15343,7 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
@@ -15397,12 +15397,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
@@ -15483,7 +15483,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P105" t="n">
@@ -15496,7 +15496,7 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
@@ -15541,12 +15541,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
@@ -15627,7 +15627,7 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P106" t="n">
@@ -15640,7 +15640,7 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
@@ -15685,12 +15685,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
@@ -15775,7 +15775,7 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -15829,12 +15829,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
@@ -15915,7 +15915,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P108" t="n">
@@ -15928,7 +15928,7 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
@@ -15973,12 +15973,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC108" t="inlineStr">
@@ -16059,7 +16059,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P109" t="n">
@@ -16072,7 +16072,7 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S109" t="inlineStr">
@@ -16117,12 +16117,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr">
@@ -16207,7 +16207,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -16261,12 +16261,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr">
@@ -16347,7 +16347,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P111" t="n">
@@ -16360,7 +16360,7 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S111" t="inlineStr">
@@ -16405,12 +16405,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr">
@@ -16491,7 +16491,7 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P112" t="n">
@@ -16504,7 +16504,7 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S112" t="inlineStr">
@@ -16549,12 +16549,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC112" t="inlineStr">
@@ -16639,7 +16639,7 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -16693,12 +16693,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr">
@@ -16783,7 +16783,7 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -16837,12 +16837,12 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr">
@@ -16927,7 +16927,7 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -16981,12 +16981,12 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr">
@@ -17071,7 +17071,7 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -17125,12 +17125,12 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr">
@@ -17215,7 +17215,7 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -17269,12 +17269,12 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
@@ -17355,7 +17355,7 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P118" t="n">
@@ -17368,7 +17368,7 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S118" t="inlineStr">
@@ -17413,12 +17413,12 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC118" t="inlineStr">
@@ -17499,7 +17499,7 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P119" t="n">
@@ -17512,7 +17512,7 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">
@@ -17557,12 +17557,12 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC119" t="inlineStr">
@@ -17647,7 +17647,7 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
@@ -17701,12 +17701,12 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC120" t="inlineStr">
@@ -17791,7 +17791,7 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
@@ -17845,12 +17845,12 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC121" t="inlineStr">
@@ -17889,7 +17889,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>E. &amp; R. G█████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>K. &amp; G. G█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -17931,7 +17931,7 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P122" t="n">
@@ -17944,7 +17944,7 @@
       </c>
       <c r="R122" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S122" t="inlineStr">
@@ -17989,17 +17989,17 @@
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>E. &amp; R. G█████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>K. &amp; G. G█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD122" t="inlineStr">
@@ -18079,7 +18079,7 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
@@ -18133,12 +18133,12 @@
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC123" t="inlineStr">
@@ -18223,7 +18223,7 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
@@ -18277,12 +18277,12 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC124" t="inlineStr">
@@ -18367,7 +18367,7 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -18421,12 +18421,12 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC125" t="inlineStr">
@@ -18507,7 +18507,7 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P126" t="n">
@@ -18520,7 +18520,7 @@
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S126" t="inlineStr">
@@ -18565,12 +18565,12 @@
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC126" t="inlineStr">
@@ -18609,7 +18609,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>E. &amp; L. S██████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>A. &amp; A. M███████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -18651,7 +18651,7 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P127" t="n">
@@ -18664,7 +18664,7 @@
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S127" t="inlineStr">
@@ -18709,17 +18709,17 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>E. &amp; L. S██████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>A. &amp; A. M███████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD127" t="inlineStr">
@@ -18799,7 +18799,7 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
@@ -18853,12 +18853,12 @@
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC128" t="inlineStr">
@@ -18939,7 +18939,7 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P129" t="n">
@@ -18952,7 +18952,7 @@
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S129" t="inlineStr">
@@ -18997,12 +18997,12 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC129" t="inlineStr">
@@ -19083,7 +19083,7 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P130" t="n">
@@ -19096,7 +19096,7 @@
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S130" t="inlineStr">
@@ -19141,12 +19141,12 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC130" t="inlineStr">
@@ -19227,7 +19227,7 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P131" t="n">
@@ -19240,7 +19240,7 @@
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S131" t="inlineStr">
@@ -19285,12 +19285,12 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC131" t="inlineStr">
@@ -19375,7 +19375,7 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
@@ -19429,12 +19429,12 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC132" t="inlineStr">
@@ -19519,7 +19519,7 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
@@ -19573,12 +19573,12 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC133" t="inlineStr">
@@ -19663,7 +19663,7 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
@@ -19717,12 +19717,12 @@
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC134" t="inlineStr">
@@ -19807,7 +19807,7 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
@@ -19861,12 +19861,12 @@
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC135" t="inlineStr">
@@ -19905,7 +19905,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>R. &amp; S. C██████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>O. &amp; C. S██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -19947,7 +19947,7 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P136" t="n">
@@ -19960,7 +19960,7 @@
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S136" t="inlineStr">
@@ -20005,17 +20005,17 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>R. &amp; S. C██████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>O. &amp; C. S██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD136" t="inlineStr">
@@ -20091,7 +20091,7 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P137" t="n">
@@ -20104,7 +20104,7 @@
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S137" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC137" t="inlineStr">
@@ -20235,7 +20235,7 @@
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P138" t="n">
@@ -20248,7 +20248,7 @@
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S138" t="inlineStr">
@@ -20293,12 +20293,12 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC138" t="inlineStr">
@@ -20379,7 +20379,7 @@
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P139" t="n">
@@ -20392,7 +20392,7 @@
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S139" t="inlineStr">
@@ -20437,12 +20437,12 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC139" t="inlineStr">
@@ -20523,7 +20523,7 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P140" t="n">
@@ -20536,7 +20536,7 @@
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S140" t="inlineStr">
@@ -20581,12 +20581,12 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC140" t="inlineStr">
@@ -20667,7 +20667,7 @@
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P141" t="n">
@@ -20680,7 +20680,7 @@
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S141" t="inlineStr">
@@ -20725,12 +20725,12 @@
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC141" t="inlineStr">
@@ -20811,7 +20811,7 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P142" t="n">
@@ -20824,7 +20824,7 @@
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S142" t="inlineStr">
@@ -20869,12 +20869,12 @@
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC142" t="inlineStr">
@@ -20959,7 +20959,7 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Q143" t="inlineStr">
         <is>
@@ -21013,12 +21013,12 @@
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC143" t="inlineStr">
@@ -21103,7 +21103,7 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q144" t="inlineStr">
         <is>
@@ -21157,12 +21157,12 @@
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC144" t="inlineStr">
@@ -21243,7 +21243,7 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P145" t="n">
@@ -21256,7 +21256,7 @@
       </c>
       <c r="R145" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S145" t="inlineStr">
@@ -21301,12 +21301,12 @@
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC145" t="inlineStr">
@@ -21391,7 +21391,7 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="Q146" t="inlineStr">
         <is>
@@ -21445,12 +21445,12 @@
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC146" t="inlineStr">
@@ -21535,7 +21535,7 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Q147" t="inlineStr">
         <is>
@@ -21589,12 +21589,12 @@
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC147" t="inlineStr">
@@ -21679,7 +21679,7 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="Q148" t="inlineStr">
         <is>
@@ -21733,12 +21733,12 @@
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC148" t="inlineStr">
@@ -21819,7 +21819,7 @@
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P149" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S149" t="inlineStr">
@@ -21877,12 +21877,12 @@
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC149" t="inlineStr">
@@ -21967,7 +21967,7 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q150" t="inlineStr">
         <is>
@@ -22021,12 +22021,12 @@
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC150" t="inlineStr">
@@ -22107,7 +22107,7 @@
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P151" t="n">
@@ -22120,7 +22120,7 @@
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S151" t="inlineStr">
@@ -22165,12 +22165,12 @@
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC151" t="inlineStr">
@@ -22255,7 +22255,7 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q152" t="inlineStr">
         <is>
@@ -22309,12 +22309,12 @@
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC152" t="inlineStr">
@@ -22395,7 +22395,7 @@
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P153" t="n">
@@ -22408,7 +22408,7 @@
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S153" t="inlineStr">
@@ -22453,12 +22453,12 @@
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC153" t="inlineStr">
@@ -22539,7 +22539,7 @@
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P154" t="n">
@@ -22552,7 +22552,7 @@
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S154" t="inlineStr">
@@ -22597,12 +22597,12 @@
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC154" t="inlineStr">
@@ -22687,7 +22687,7 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q155" t="inlineStr">
         <is>
@@ -22741,12 +22741,12 @@
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC155" t="inlineStr">
@@ -22831,7 +22831,7 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
@@ -22885,12 +22885,12 @@
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC156" t="inlineStr">
@@ -22929,7 +22929,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>S. &amp; M. D████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>V. &amp; L. D████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -22971,7 +22971,7 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P157" t="n">
@@ -22984,7 +22984,7 @@
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S157" t="inlineStr">
@@ -23029,17 +23029,17 @@
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>S. &amp; M. D████ [SUBSCRIBER KEY REQUIRED]</t>
+          <t>V. &amp; L. D████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="AD157" t="inlineStr">
@@ -23119,7 +23119,7 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q158" t="inlineStr">
         <is>
@@ -23173,12 +23173,12 @@
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC158" t="inlineStr">
@@ -23263,7 +23263,7 @@
         </is>
       </c>
       <c r="P159" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Q159" t="inlineStr">
         <is>
@@ -23317,12 +23317,12 @@
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC159" t="inlineStr">
@@ -23403,7 +23403,7 @@
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P160" t="n">
@@ -23416,7 +23416,7 @@
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S160" t="inlineStr">
@@ -23461,12 +23461,12 @@
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC160" t="inlineStr">
@@ -23551,7 +23551,7 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Q161" t="inlineStr">
         <is>
@@ -23605,12 +23605,12 @@
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC161" t="inlineStr">
@@ -23695,7 +23695,7 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q162" t="inlineStr">
         <is>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC162" t="inlineStr">
@@ -23839,7 +23839,7 @@
         </is>
       </c>
       <c r="P163" t="n">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Q163" t="inlineStr">
         <is>
@@ -23893,12 +23893,12 @@
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC163" t="inlineStr">
@@ -23979,7 +23979,7 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P164" t="n">
@@ -23992,7 +23992,7 @@
       </c>
       <c r="R164" t="inlineStr">
         <is>
-          <t>2028-10-29</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="S164" t="inlineStr">
@@ -24037,12 +24037,12 @@
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:37Z</t>
+          <t>2026-10-31T10:21:05Z</t>
         </is>
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC164" t="inlineStr">
@@ -24127,7 +24127,7 @@
         </is>
       </c>
       <c r="P165" t="n">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="Q165" t="inlineStr">
         <is>
@@ -24181,12 +24181,12 @@
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC165" t="inlineStr">
@@ -24271,7 +24271,7 @@
         </is>
       </c>
       <c r="P166" t="n">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="Q166" t="inlineStr">
         <is>
@@ -24325,12 +24325,12 @@
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC166" t="inlineStr">
@@ -24415,7 +24415,7 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="Q167" t="inlineStr">
         <is>
@@ -24469,12 +24469,12 @@
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC167" t="inlineStr">
@@ -24559,7 +24559,7 @@
         </is>
       </c>
       <c r="P168" t="n">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="Q168" t="inlineStr">
         <is>
@@ -24613,12 +24613,12 @@
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC168" t="inlineStr">
@@ -24703,7 +24703,7 @@
         </is>
       </c>
       <c r="P169" t="n">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="Q169" t="inlineStr">
         <is>
@@ -24757,12 +24757,12 @@
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC169" t="inlineStr">
@@ -24847,7 +24847,7 @@
         </is>
       </c>
       <c r="P170" t="n">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="Q170" t="inlineStr">
         <is>
@@ -24901,12 +24901,12 @@
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:36Z</t>
+          <t>2026-10-31T10:21:04Z</t>
         </is>
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC170" t="inlineStr">
